--- a/artfynd/A 23373-2026 artfynd.xlsx
+++ b/artfynd/A 23373-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,35 +675,38 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>134587770</v>
+        <v>134587897</v>
       </c>
       <c r="B2" t="n">
-        <v>103907</v>
+        <v>79373</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>223284</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Sälg</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Bredänget, Nb</t>
@@ -745,7 +748,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +758,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -764,6 +767,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -775,10 +779,117 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
+          <t>Maj Aspebo, Linnea  Isaksson</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>134587770</v>
+      </c>
+      <c r="B3" t="n">
+        <v>103907</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>223284</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Sälg</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Bredänget, Nb</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>850729</v>
+      </c>
+      <c r="R3" t="n">
+        <v>7370099</v>
+      </c>
+      <c r="S3" t="n">
+        <v>2</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>10:53</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>10:53</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
           <t>Maj Aspebo</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr"/>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Maj Aspebo</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 23373-2026 artfynd.xlsx
+++ b/artfynd/A 23373-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -786,48 +786,55 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>134587770</v>
+        <v>135255657</v>
       </c>
       <c r="B3" t="n">
-        <v>103907</v>
+        <v>57975</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>223284</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Sälg</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Bredänget, Nb</t>
+          <t>Svartbyn, Nb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>850729</v>
+        <v>850653</v>
       </c>
       <c r="R3" t="n">
-        <v>7370099</v>
+        <v>7370002</v>
       </c>
       <c r="S3" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -851,22 +858,27 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>16:07</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -881,15 +893,241 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Elin Kannerby, Linnea  Isaksson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>135255658</v>
+      </c>
+      <c r="B4" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Svartbyn, Nb</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>850651</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7370010</v>
+      </c>
+      <c r="S4" t="n">
+        <v>6</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>16:13</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>16:13</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Elin Kannerby, Linnea  Isaksson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>134587770</v>
+      </c>
+      <c r="B5" t="n">
+        <v>103907</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>223284</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Sälg</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Bredänget, Nb</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>850729</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7370099</v>
+      </c>
+      <c r="S5" t="n">
+        <v>2</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>10:53</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>10:53</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
           <t>Maj Aspebo</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
+      <c r="AX5" t="inlineStr">
         <is>
           <t>Maj Aspebo</t>
         </is>
       </c>
-      <c r="AY3" t="inlineStr"/>
+      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 23373-2026 artfynd.xlsx
+++ b/artfynd/A 23373-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1024,32 +1024,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>134587770</v>
+        <v>135269266</v>
       </c>
       <c r="B5" t="n">
-        <v>103907</v>
+        <v>99195</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>223284</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Sälg</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1089,22 +1089,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1128,6 +1128,113 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>134587770</v>
+      </c>
+      <c r="B6" t="n">
+        <v>103907</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>223284</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Sälg</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Bredänget, Nb</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>850729</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7370099</v>
+      </c>
+      <c r="S6" t="n">
+        <v>2</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>10:53</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>10:53</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Maj Aspebo</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Maj Aspebo</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 23373-2026 artfynd.xlsx
+++ b/artfynd/A 23373-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -783,6 +788,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134587897</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -902,6 +912,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135255657</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1021,6 +1036,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135255658</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1128,6 +1148,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135269266</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1235,8 +1260,20 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134587770</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 23373-2026 artfynd.xlsx
+++ b/artfynd/A 23373-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ6"/>
+  <dimension ref="A1:AZ12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,38 +680,35 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>134587897</v>
+        <v>135268965</v>
       </c>
       <c r="B2" t="n">
-        <v>79373</v>
+        <v>106492</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>674</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Myskmåra</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Galium triflorum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Michx.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Bredänget, Nb</t>
@@ -748,22 +745,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -772,7 +769,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -784,67 +780,63 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Maj Aspebo, Linnea  Isaksson</t>
+          <t>Maj Aspebo</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134587897</t>
+          <t>https://artportalen.se/Sighting/135268965</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>135255657</v>
+        <v>134587897</v>
       </c>
       <c r="B3" t="n">
-        <v>57975</v>
+        <v>79373</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Svartbyn, Nb</t>
+          <t>Bredänget, Nb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>850653</v>
+        <v>850729</v>
       </c>
       <c r="R3" t="n">
-        <v>7370002</v>
+        <v>7370099</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -868,27 +860,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>16:07</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -897,78 +884,75 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Maj Aspebo</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Linnea  Isaksson</t>
+          <t>Maj Aspebo, Linnea  Isaksson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135255657</t>
+          <t>https://artportalen.se/Sighting/134587897</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>135255658</v>
+        <v>135605687</v>
       </c>
       <c r="B4" t="n">
-        <v>57975</v>
+        <v>79435</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6434</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Svartbyn, Nb</t>
+          <t>Nästlav, Nb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>850651</v>
+        <v>850598</v>
       </c>
       <c r="R4" t="n">
-        <v>7370010</v>
+        <v>7370090</v>
       </c>
       <c r="S4" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -992,27 +976,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>16:13</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>16:13</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1021,71 +990,79 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Linnea  Isaksson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Linnea  Isaksson</t>
+          <t>Linnea  Isaksson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135255658</t>
+          <t>https://artportalen.se/Sighting/135605687</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>135269266</v>
+        <v>135255657</v>
       </c>
       <c r="B5" t="n">
-        <v>99195</v>
+        <v>57980</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Bredänget, Nb</t>
+          <t>Svartbyn, Nb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>850729</v>
+        <v>850653</v>
       </c>
       <c r="R5" t="n">
-        <v>7370099</v>
+        <v>7370002</v>
       </c>
       <c r="S5" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1109,22 +1086,27 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>16:07</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1139,65 +1121,72 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Maj Aspebo</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Maj Aspebo</t>
+          <t>Elin Kannerby, Linnea  Isaksson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135269266</t>
+          <t>https://artportalen.se/Sighting/135255657</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>134587770</v>
+        <v>135255658</v>
       </c>
       <c r="B6" t="n">
-        <v>103907</v>
+        <v>57980</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>223284</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Sälg</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Bredänget, Nb</t>
+          <t>Svartbyn, Nb</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>850729</v>
+        <v>850651</v>
       </c>
       <c r="R6" t="n">
-        <v>7370099</v>
+        <v>7370010</v>
       </c>
       <c r="S6" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1221,22 +1210,27 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>16:13</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1251,16 +1245,686 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Maj Aspebo</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Maj Aspebo</t>
+          <t>Elin Kannerby, Linnea  Isaksson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135255658</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>135268372</v>
+      </c>
+      <c r="B7" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Bredänget, Nb</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>850729</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7370099</v>
+      </c>
+      <c r="S7" t="n">
+        <v>2</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>11:44</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>11:44</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Maj Aspebo</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Maj Aspebo</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135268372</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>135605668</v>
+      </c>
+      <c r="B8" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Västra Svartbyn, Nb</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>850658</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7370037</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Linnea  Isaksson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Linnea  Isaksson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135605668</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>135605674</v>
+      </c>
+      <c r="B9" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Västra Svartbyn, Nb</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>850638</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7370073</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Linnea  Isaksson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Linnea  Isaksson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135605674</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>135269266</v>
+      </c>
+      <c r="B10" t="n">
+        <v>99242</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Bredänget, Nb</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>850729</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7370099</v>
+      </c>
+      <c r="S10" t="n">
+        <v>2</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>12:28</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>12:28</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Maj Aspebo</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Maj Aspebo</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135269266</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>135605684</v>
+      </c>
+      <c r="B11" t="n">
+        <v>99242</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Bredänget, Nb</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>850739</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7370043</v>
+      </c>
+      <c r="S11" t="n">
+        <v>25</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Linnea  Isaksson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Linnea  Isaksson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135605684</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>134587770</v>
+      </c>
+      <c r="B12" t="n">
+        <v>103907</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>223284</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Sälg</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Bredänget, Nb</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>850729</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7370099</v>
+      </c>
+      <c r="S12" t="n">
+        <v>2</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>10:53</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>10:53</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Maj Aspebo</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Maj Aspebo</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/134587770</t>
         </is>
@@ -1273,6 +1937,12 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 23373-2026 artfynd.xlsx
+++ b/artfynd/A 23373-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135268965</v>
       </c>
       <c r="B2" t="n">
-        <v>106492</v>
+        <v>106519</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -911,7 +911,7 @@
         <v>135605687</v>
       </c>
       <c r="B4" t="n">
-        <v>79435</v>
+        <v>79462</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1604,7 +1604,7 @@
         <v>135269266</v>
       </c>
       <c r="B10" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1716,7 +1716,7 @@
         <v>135605684</v>
       </c>
       <c r="B11" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 23373-2026 artfynd.xlsx
+++ b/artfynd/A 23373-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ12"/>
+  <dimension ref="A1:AZ13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1820,32 +1820,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>134587770</v>
+        <v>135718208</v>
       </c>
       <c r="B12" t="n">
-        <v>103907</v>
+        <v>99269</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>223284</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Sälg</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1855,13 +1855,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>850729</v>
+        <v>850717</v>
       </c>
       <c r="R12" t="n">
-        <v>7370099</v>
+        <v>7370051</v>
       </c>
       <c r="S12" t="n">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1885,22 +1885,22 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1915,16 +1915,128 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Maj Aspebo</t>
+          <t>Brjan Xotta</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Maj Aspebo</t>
+          <t>Brjan Xotta</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135718208</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>134587770</v>
+      </c>
+      <c r="B13" t="n">
+        <v>103907</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>223284</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Sälg</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Bredänget, Nb</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>850729</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7370099</v>
+      </c>
+      <c r="S13" t="n">
+        <v>2</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>10:53</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>10:53</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Maj Aspebo</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Maj Aspebo</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/134587770</t>
         </is>
@@ -1943,6 +2055,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 23373-2026 artfynd.xlsx
+++ b/artfynd/A 23373-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ3"/>
+  <dimension ref="A1:AZ16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,38 +680,35 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>134587897</v>
+        <v>135268965</v>
       </c>
       <c r="B2" t="n">
-        <v>79373</v>
+        <v>106524</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>674</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Myskmåra</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Galium triflorum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Michx.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Bredänget, Nb</t>
@@ -748,22 +745,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -772,7 +769,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -784,22 +780,22 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Maj Aspebo, Linnea  Isaksson</t>
+          <t>Maj Aspebo</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134587897</t>
+          <t>https://artportalen.se/Sighting/135268965</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>134587770</v>
+        <v>135819545</v>
       </c>
       <c r="B3" t="n">
-        <v>103907</v>
+        <v>92273</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -807,37 +803,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>223284</v>
+        <v>3298</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Sälg</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Bredänget, Nb</t>
+          <t>Bredänget, Bredänget, Nb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>850729</v>
+        <v>850682</v>
       </c>
       <c r="R3" t="n">
-        <v>7370099</v>
+        <v>7370041</v>
       </c>
       <c r="S3" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -861,22 +857,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>10:53</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>10:53</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -891,16 +877,1472 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Maj Aspebo</t>
+          <t>Arvid de Jong</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Maj Aspebo</t>
+          <t>Arvid de Jong</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135819545</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>134587897</v>
+      </c>
+      <c r="B4" t="n">
+        <v>79373</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Bredänget, Nb</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>850729</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7370099</v>
+      </c>
+      <c r="S4" t="n">
+        <v>2</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>11:02</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>11:02</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Maj Aspebo</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Maj Aspebo, Linnea  Isaksson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134587897</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>135605687</v>
+      </c>
+      <c r="B5" t="n">
+        <v>79465</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>6434</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Nästlav</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Bryoria furcellata</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Nästlav, Nb</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>850598</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7370090</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Linnea  Isaksson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Linnea  Isaksson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135605687</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>135255657</v>
+      </c>
+      <c r="B6" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Svartbyn, Nb</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>850653</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7370002</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>16:07</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>16:07</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Elin Kannerby, Linnea  Isaksson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135255657</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>135255658</v>
+      </c>
+      <c r="B7" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Svartbyn, Nb</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>850651</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7370010</v>
+      </c>
+      <c r="S7" t="n">
+        <v>6</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>16:13</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>16:13</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Elin Kannerby, Linnea  Isaksson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135255658</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>135268372</v>
+      </c>
+      <c r="B8" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Bredänget, Nb</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>850729</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7370099</v>
+      </c>
+      <c r="S8" t="n">
+        <v>2</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>11:44</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>11:44</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Maj Aspebo</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Maj Aspebo</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135268372</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>135605668</v>
+      </c>
+      <c r="B9" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Västra Svartbyn, Nb</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>850658</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7370037</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Linnea  Isaksson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Linnea  Isaksson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135605668</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>135605674</v>
+      </c>
+      <c r="B10" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Västra Svartbyn, Nb</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>850638</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7370073</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Linnea  Isaksson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Linnea  Isaksson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135605674</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>135819444</v>
+      </c>
+      <c r="B11" t="n">
+        <v>5201</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Bredänget, Bredänget, Nb</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>850692</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7370029</v>
+      </c>
+      <c r="S11" t="n">
+        <v>3</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Arvid de Jong</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Arvid de Jong</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135819444</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>135819354</v>
+      </c>
+      <c r="B12" t="n">
+        <v>8450</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>106554</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Björksplintborre</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Scolytus ratzeburgii</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Bredänget, Bredänget, Nb</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>850709</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7370035</v>
+      </c>
+      <c r="S12" t="n">
+        <v>3</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Arvid de Jong</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Arvid de Jong</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135819354</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>135269266</v>
+      </c>
+      <c r="B13" t="n">
+        <v>99274</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Bredänget, Nb</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>850729</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7370099</v>
+      </c>
+      <c r="S13" t="n">
+        <v>2</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>12:28</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>12:28</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Maj Aspebo</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Maj Aspebo</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135269266</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>135605684</v>
+      </c>
+      <c r="B14" t="n">
+        <v>99274</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Bredänget, Nb</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>850739</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7370043</v>
+      </c>
+      <c r="S14" t="n">
+        <v>25</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Linnea  Isaksson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Linnea  Isaksson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135605684</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>135718208</v>
+      </c>
+      <c r="B15" t="n">
+        <v>99274</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Bredänget, Nb</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>850717</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7370051</v>
+      </c>
+      <c r="S15" t="n">
+        <v>25</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>13:41</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>13:41</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Brjan Xotta</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Brjan Xotta</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135718208</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>134587770</v>
+      </c>
+      <c r="B16" t="n">
+        <v>103907</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>223284</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Sälg</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Bredänget, Nb</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>850729</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7370099</v>
+      </c>
+      <c r="S16" t="n">
+        <v>2</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>10:53</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>10:53</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Maj Aspebo</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Maj Aspebo</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/134587770</t>
         </is>
@@ -910,6 +2352,19 @@
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 23373-2026 artfynd.xlsx
+++ b/artfynd/A 23373-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135268965</v>
       </c>
       <c r="B2" t="n">
-        <v>106524</v>
+        <v>106526</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135819545</v>
       </c>
       <c r="B3" t="n">
-        <v>92273</v>
+        <v>92275</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1910,7 +1910,7 @@
         <v>135269266</v>
       </c>
       <c r="B13" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2022,7 +2022,7 @@
         <v>135605684</v>
       </c>
       <c r="B14" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2129,7 +2129,7 @@
         <v>135718208</v>
       </c>
       <c r="B15" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 23373-2026 artfynd.xlsx
+++ b/artfynd/A 23373-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ16"/>
+  <dimension ref="A1:AZ12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1010,51 +1010,55 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>135605687</v>
+        <v>135255657</v>
       </c>
       <c r="B5" t="n">
-        <v>79465</v>
+        <v>57980</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6434</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Nästlav, Nb</t>
+          <t>Svartbyn, Nb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>850598</v>
+        <v>850653</v>
       </c>
       <c r="R5" t="n">
-        <v>7370090</v>
+        <v>7370002</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1078,12 +1082,27 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>16:07</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1092,31 +1111,30 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Linnea  Isaksson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Linnea  Isaksson</t>
+          <t>Elin Kannerby, Linnea  Isaksson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135605687</t>
+          <t>https://artportalen.se/Sighting/135255657</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>135255657</v>
+        <v>135255658</v>
       </c>
       <c r="B6" t="n">
         <v>57980</v>
@@ -1158,13 +1176,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>850653</v>
+        <v>850651</v>
       </c>
       <c r="R6" t="n">
-        <v>7370002</v>
+        <v>7370010</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1193,7 +1211,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1203,7 +1221,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1234,13 +1252,13 @@
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135255657</t>
+          <t>https://artportalen.se/Sighting/135255658</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>135255658</v>
+        <v>135268372</v>
       </c>
       <c r="B7" t="n">
         <v>57980</v>
@@ -1269,26 +1287,19 @@
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Svartbyn, Nb</t>
+          <t>Bredänget, Nb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>850651</v>
+        <v>850729</v>
       </c>
       <c r="R7" t="n">
-        <v>7370010</v>
+        <v>7370099</v>
       </c>
       <c r="S7" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1312,27 +1323,27 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1347,44 +1358,44 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Maj Aspebo</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Linnea  Isaksson</t>
+          <t>Maj Aspebo</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135255658</t>
+          <t>https://artportalen.se/Sighting/135268372</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>135268372</v>
+        <v>135819444</v>
       </c>
       <c r="B8" t="n">
-        <v>57980</v>
+        <v>5201</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>105930</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1395,17 +1406,17 @@
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Bredänget, Nb</t>
+          <t>Bredänget, Bredänget, Nb</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>850729</v>
+        <v>850692</v>
       </c>
       <c r="R8" t="n">
-        <v>7370099</v>
+        <v>7370029</v>
       </c>
       <c r="S8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1429,27 +1440,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>11:44</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>11:44</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1464,69 +1460,65 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Maj Aspebo</t>
+          <t>Arvid de Jong</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Maj Aspebo</t>
+          <t>Arvid de Jong</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135268372</t>
+          <t>https://artportalen.se/Sighting/135819444</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>135605668</v>
+        <v>135819354</v>
       </c>
       <c r="B9" t="n">
-        <v>57980</v>
+        <v>8450</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>106554</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Västra Svartbyn, Nb</t>
+          <t>Bredänget, Bredänget, Nb</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>850658</v>
+        <v>850709</v>
       </c>
       <c r="R9" t="n">
-        <v>7370037</v>
+        <v>7370035</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1550,17 +1542,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1575,69 +1562,65 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Linnea  Isaksson</t>
+          <t>Arvid de Jong</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Linnea  Isaksson</t>
+          <t>Arvid de Jong</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135605668</t>
+          <t>https://artportalen.se/Sighting/135819354</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>135605674</v>
+        <v>135269266</v>
       </c>
       <c r="B10" t="n">
-        <v>57980</v>
+        <v>99276</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Västra Svartbyn, Nb</t>
+          <t>Bredänget, Nb</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>850638</v>
+        <v>850729</v>
       </c>
       <c r="R10" t="n">
-        <v>7370073</v>
+        <v>7370099</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1664,14 +1647,19 @@
           <t>2026-07-20</t>
         </is>
       </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>12:28</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2026-07-20</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1686,65 +1674,65 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Linnea  Isaksson</t>
+          <t>Maj Aspebo</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Linnea  Isaksson</t>
+          <t>Maj Aspebo</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135605674</t>
+          <t>https://artportalen.se/Sighting/135269266</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>135819444</v>
+        <v>135718208</v>
       </c>
       <c r="B11" t="n">
-        <v>5201</v>
+        <v>99276</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>105930</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Bredänget, Bredänget, Nb</t>
+          <t>Bredänget, Nb</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>850692</v>
+        <v>850717</v>
       </c>
       <c r="R11" t="n">
-        <v>7370029</v>
+        <v>7370051</v>
       </c>
       <c r="S11" t="n">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1768,12 +1756,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1788,27 +1786,27 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Arvid de Jong</t>
+          <t>Brjan Xotta</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Arvid de Jong</t>
+          <t>Brjan Xotta</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135819444</t>
+          <t>https://artportalen.se/Sighting/135718208</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>135819354</v>
+        <v>134587770</v>
       </c>
       <c r="B12" t="n">
-        <v>8450</v>
+        <v>103907</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1816,37 +1814,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>106554</v>
+        <v>223284</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Sälg</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Bredänget, Bredänget, Nb</t>
+          <t>Bredänget, Nb</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>850709</v>
+        <v>850729</v>
       </c>
       <c r="R12" t="n">
-        <v>7370035</v>
+        <v>7370099</v>
       </c>
       <c r="S12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1870,12 +1868,22 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1890,459 +1898,16 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Arvid de Jong</t>
+          <t>Maj Aspebo</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Arvid de Jong</t>
+          <t>Maj Aspebo</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135819354</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>135269266</v>
-      </c>
-      <c r="B13" t="n">
-        <v>99276</v>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E13" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>Bredänget, Nb</t>
-        </is>
-      </c>
-      <c r="Q13" t="n">
-        <v>850729</v>
-      </c>
-      <c r="R13" t="n">
-        <v>7370099</v>
-      </c>
-      <c r="S13" t="n">
-        <v>2</v>
-      </c>
-      <c r="T13" t="inlineStr">
-        <is>
-          <t>Norrbotten</t>
-        </is>
-      </c>
-      <c r="U13" t="inlineStr">
-        <is>
-          <t>Överkalix</t>
-        </is>
-      </c>
-      <c r="V13" t="inlineStr">
-        <is>
-          <t>Norrbotten</t>
-        </is>
-      </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>Överkalix</t>
-        </is>
-      </c>
-      <c r="Y13" t="inlineStr">
-        <is>
-          <t>2026-07-20</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>12:28</t>
-        </is>
-      </c>
-      <c r="AA13" t="inlineStr">
-        <is>
-          <t>2026-07-20</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>12:28</t>
-        </is>
-      </c>
-      <c r="AD13" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE13" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG13" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT13" t="inlineStr"/>
-      <c r="AW13" t="inlineStr">
-        <is>
-          <t>Maj Aspebo</t>
-        </is>
-      </c>
-      <c r="AX13" t="inlineStr">
-        <is>
-          <t>Maj Aspebo</t>
-        </is>
-      </c>
-      <c r="AY13" t="inlineStr"/>
-      <c r="AZ13" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135269266</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>135605684</v>
-      </c>
-      <c r="B14" t="n">
-        <v>99276</v>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E14" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>Bredänget, Nb</t>
-        </is>
-      </c>
-      <c r="Q14" t="n">
-        <v>850739</v>
-      </c>
-      <c r="R14" t="n">
-        <v>7370043</v>
-      </c>
-      <c r="S14" t="n">
-        <v>25</v>
-      </c>
-      <c r="T14" t="inlineStr">
-        <is>
-          <t>Norrbotten</t>
-        </is>
-      </c>
-      <c r="U14" t="inlineStr">
-        <is>
-          <t>Överkalix</t>
-        </is>
-      </c>
-      <c r="V14" t="inlineStr">
-        <is>
-          <t>Norrbotten</t>
-        </is>
-      </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>Överkalix</t>
-        </is>
-      </c>
-      <c r="Y14" t="inlineStr">
-        <is>
-          <t>2026-08-02</t>
-        </is>
-      </c>
-      <c r="AA14" t="inlineStr">
-        <is>
-          <t>2026-08-02</t>
-        </is>
-      </c>
-      <c r="AD14" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE14" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF14" t="inlineStr"/>
-      <c r="AG14" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT14" t="inlineStr"/>
-      <c r="AW14" t="inlineStr">
-        <is>
-          <t>Linnea  Isaksson</t>
-        </is>
-      </c>
-      <c r="AX14" t="inlineStr">
-        <is>
-          <t>Linnea  Isaksson</t>
-        </is>
-      </c>
-      <c r="AY14" t="inlineStr"/>
-      <c r="AZ14" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135605684</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>135718208</v>
-      </c>
-      <c r="B15" t="n">
-        <v>99276</v>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E15" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>Bredänget, Nb</t>
-        </is>
-      </c>
-      <c r="Q15" t="n">
-        <v>850717</v>
-      </c>
-      <c r="R15" t="n">
-        <v>7370051</v>
-      </c>
-      <c r="S15" t="n">
-        <v>25</v>
-      </c>
-      <c r="T15" t="inlineStr">
-        <is>
-          <t>Norrbotten</t>
-        </is>
-      </c>
-      <c r="U15" t="inlineStr">
-        <is>
-          <t>Överkalix</t>
-        </is>
-      </c>
-      <c r="V15" t="inlineStr">
-        <is>
-          <t>Norrbotten</t>
-        </is>
-      </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>Överkalix</t>
-        </is>
-      </c>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>13:41</t>
-        </is>
-      </c>
-      <c r="AA15" t="inlineStr">
-        <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>13:41</t>
-        </is>
-      </c>
-      <c r="AD15" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE15" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG15" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT15" t="inlineStr"/>
-      <c r="AW15" t="inlineStr">
-        <is>
-          <t>Brjan Xotta</t>
-        </is>
-      </c>
-      <c r="AX15" t="inlineStr">
-        <is>
-          <t>Brjan Xotta</t>
-        </is>
-      </c>
-      <c r="AY15" t="inlineStr"/>
-      <c r="AZ15" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135718208</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>134587770</v>
-      </c>
-      <c r="B16" t="n">
-        <v>103907</v>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E16" t="n">
-        <v>223284</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>Sälg</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>Bredänget, Nb</t>
-        </is>
-      </c>
-      <c r="Q16" t="n">
-        <v>850729</v>
-      </c>
-      <c r="R16" t="n">
-        <v>7370099</v>
-      </c>
-      <c r="S16" t="n">
-        <v>2</v>
-      </c>
-      <c r="T16" t="inlineStr">
-        <is>
-          <t>Norrbotten</t>
-        </is>
-      </c>
-      <c r="U16" t="inlineStr">
-        <is>
-          <t>Överkalix</t>
-        </is>
-      </c>
-      <c r="V16" t="inlineStr">
-        <is>
-          <t>Norrbotten</t>
-        </is>
-      </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>Överkalix</t>
-        </is>
-      </c>
-      <c r="Y16" t="inlineStr">
-        <is>
-          <t>2026-06-23</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>10:53</t>
-        </is>
-      </c>
-      <c r="AA16" t="inlineStr">
-        <is>
-          <t>2026-06-23</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>10:53</t>
-        </is>
-      </c>
-      <c r="AD16" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE16" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG16" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT16" t="inlineStr"/>
-      <c r="AW16" t="inlineStr">
-        <is>
-          <t>Maj Aspebo</t>
-        </is>
-      </c>
-      <c r="AX16" t="inlineStr">
-        <is>
-          <t>Maj Aspebo</t>
-        </is>
-      </c>
-      <c r="AY16" t="inlineStr"/>
-      <c r="AZ16" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/134587770</t>
         </is>
@@ -2361,10 +1926,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 23373-2026 artfynd.xlsx
+++ b/artfynd/A 23373-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ12"/>
+  <dimension ref="A1:AZ16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1010,55 +1010,51 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>135255657</v>
+        <v>135605687</v>
       </c>
       <c r="B5" t="n">
-        <v>57980</v>
+        <v>79465</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6434</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Svartbyn, Nb</t>
+          <t>Nästlav, Nb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>850653</v>
+        <v>850598</v>
       </c>
       <c r="R5" t="n">
-        <v>7370002</v>
+        <v>7370090</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1082,27 +1078,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>16:07</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>16:07</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1111,30 +1092,31 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Linnea  Isaksson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Linnea  Isaksson</t>
+          <t>Linnea  Isaksson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135255657</t>
+          <t>https://artportalen.se/Sighting/135605687</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>135255658</v>
+        <v>135255657</v>
       </c>
       <c r="B6" t="n">
         <v>57980</v>
@@ -1176,13 +1158,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>850651</v>
+        <v>850653</v>
       </c>
       <c r="R6" t="n">
-        <v>7370010</v>
+        <v>7370002</v>
       </c>
       <c r="S6" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1211,7 +1193,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1221,7 +1203,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1252,13 +1234,13 @@
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135255658</t>
+          <t>https://artportalen.se/Sighting/135255657</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>135268372</v>
+        <v>135255658</v>
       </c>
       <c r="B7" t="n">
         <v>57980</v>
@@ -1287,19 +1269,26 @@
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Bredänget, Nb</t>
+          <t>Svartbyn, Nb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>850729</v>
+        <v>850651</v>
       </c>
       <c r="R7" t="n">
-        <v>7370099</v>
+        <v>7370010</v>
       </c>
       <c r="S7" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1323,27 +1312,27 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1358,44 +1347,44 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Maj Aspebo</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Maj Aspebo</t>
+          <t>Elin Kannerby, Linnea  Isaksson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135268372</t>
+          <t>https://artportalen.se/Sighting/135255658</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>135819444</v>
+        <v>135268372</v>
       </c>
       <c r="B8" t="n">
-        <v>5201</v>
+        <v>57980</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>105930</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1406,17 +1395,17 @@
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Bredänget, Bredänget, Nb</t>
+          <t>Bredänget, Nb</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>850692</v>
+        <v>850729</v>
       </c>
       <c r="R8" t="n">
-        <v>7370029</v>
+        <v>7370099</v>
       </c>
       <c r="S8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1440,12 +1429,27 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>11:44</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1460,65 +1464,69 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Arvid de Jong</t>
+          <t>Maj Aspebo</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Arvid de Jong</t>
+          <t>Maj Aspebo</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135819444</t>
+          <t>https://artportalen.se/Sighting/135268372</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>135819354</v>
+        <v>135605668</v>
       </c>
       <c r="B9" t="n">
-        <v>8450</v>
+        <v>57980</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>106554</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Bredänget, Bredänget, Nb</t>
+          <t>Västra Svartbyn, Nb</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>850709</v>
+        <v>850658</v>
       </c>
       <c r="R9" t="n">
-        <v>7370035</v>
+        <v>7370037</v>
       </c>
       <c r="S9" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1542,12 +1550,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1562,65 +1575,69 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Arvid de Jong</t>
+          <t>Linnea  Isaksson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Arvid de Jong</t>
+          <t>Linnea  Isaksson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135819354</t>
+          <t>https://artportalen.se/Sighting/135605668</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>135269266</v>
+        <v>135605674</v>
       </c>
       <c r="B10" t="n">
-        <v>99276</v>
+        <v>57980</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Bredänget, Nb</t>
+          <t>Västra Svartbyn, Nb</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>850729</v>
+        <v>850638</v>
       </c>
       <c r="R10" t="n">
-        <v>7370099</v>
+        <v>7370073</v>
       </c>
       <c r="S10" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1647,19 +1664,14 @@
           <t>2026-07-20</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>12:28</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2026-07-20</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>12:28</t>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1674,65 +1686,65 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Maj Aspebo</t>
+          <t>Linnea  Isaksson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Maj Aspebo</t>
+          <t>Linnea  Isaksson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135269266</t>
+          <t>https://artportalen.se/Sighting/135605674</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>135718208</v>
+        <v>135819444</v>
       </c>
       <c r="B11" t="n">
-        <v>99276</v>
+        <v>5201</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>105930</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Bredänget, Nb</t>
+          <t>Bredänget, Bredänget, Nb</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>850717</v>
+        <v>850692</v>
       </c>
       <c r="R11" t="n">
-        <v>7370051</v>
+        <v>7370029</v>
       </c>
       <c r="S11" t="n">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1756,22 +1768,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>13:41</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>13:41</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1786,27 +1788,27 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Brjan Xotta</t>
+          <t>Arvid de Jong</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Brjan Xotta</t>
+          <t>Arvid de Jong</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135718208</t>
+          <t>https://artportalen.se/Sighting/135819444</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>134587770</v>
+        <v>135819354</v>
       </c>
       <c r="B12" t="n">
-        <v>103907</v>
+        <v>8450</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1814,37 +1816,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>223284</v>
+        <v>106554</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Sälg</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Bredänget, Nb</t>
+          <t>Bredänget, Bredänget, Nb</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>850729</v>
+        <v>850709</v>
       </c>
       <c r="R12" t="n">
-        <v>7370099</v>
+        <v>7370035</v>
       </c>
       <c r="S12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1868,22 +1870,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>10:53</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>10:53</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1898,16 +1890,459 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Maj Aspebo</t>
+          <t>Arvid de Jong</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Maj Aspebo</t>
+          <t>Arvid de Jong</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135819354</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>135269266</v>
+      </c>
+      <c r="B13" t="n">
+        <v>99276</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Bredänget, Nb</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>850729</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7370099</v>
+      </c>
+      <c r="S13" t="n">
+        <v>2</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>12:28</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>12:28</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Maj Aspebo</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Maj Aspebo</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135269266</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>135605684</v>
+      </c>
+      <c r="B14" t="n">
+        <v>99276</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Bredänget, Nb</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>850739</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7370043</v>
+      </c>
+      <c r="S14" t="n">
+        <v>25</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Linnea  Isaksson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Linnea  Isaksson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135605684</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>135718208</v>
+      </c>
+      <c r="B15" t="n">
+        <v>99276</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Bredänget, Nb</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>850717</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7370051</v>
+      </c>
+      <c r="S15" t="n">
+        <v>25</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>13:41</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>13:41</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Brjan Xotta</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Brjan Xotta</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135718208</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>134587770</v>
+      </c>
+      <c r="B16" t="n">
+        <v>103907</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>223284</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Sälg</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Bredänget, Nb</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>850729</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7370099</v>
+      </c>
+      <c r="S16" t="n">
+        <v>2</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>10:53</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>10:53</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Maj Aspebo</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Maj Aspebo</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/134587770</t>
         </is>
@@ -1926,6 +2361,10 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
